--- a/report/bug_list.xlsx
+++ b/report/bug_list.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Exploit code</t>
+          <t>Exploit code / PoC</t>
         </is>
       </c>
     </row>
@@ -526,32 +526,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AES_KEY_SHARE0/1 and AES_DATA_IN registers return real key/data on MMIO read instead of hardwired 0; raw AES key can be read back and both shares XORed to recover it in the clear.</t>
+          <t>AES_KEY_SHARE0/1 registers return the real stored key word on MMIO read instead of hardwired 0; raw AES key recoverable by XOR-ing the two shares.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>src/aes/rtl/aes_reg_top.sv, read-mux addr_hit[1..16], addr_hit[21..24]</t>
+          <t>src/aes/rtl/aes_reg_top.sv, read-mux addr_hit[1..16]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream caliptra-rtl v2.1.2 (evidence/01_...diff); manual datapath trace of reg2hw.key_share0/1.q into reg_rdata_next</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED with a Verilator testbench reproducing the exact patched mux line</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Complete disclosure of AES key material to any software/DMA agent with register read access; breaks confidentiality of any secret protected by the hardware AES engine (incl. OCP-Lock/DICE-derived keys)</t>
+          <t>Complete disclosure of AES key material to any software/DMA agent with register read access</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Local software/firmware executing on the SoC with MMIO read access to the AES peripheral; no elevated privilege required</t>
+          <t>Local software/firmware with MMIO read access to the AES peripheral; no elevated privilege required</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Restore hardwired 0 return for KEY_SHARE0/1 and DATA_IN read paths in the auto-generated reg_top (fix reggen template/RDL and regenerate); add SVA that these addresses always read 0</t>
+          <t>Restore hardwired 0 return for KEY_SHARE0/1 (and DATA_IN) read paths; add SVA that these addresses always read 0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>for i in range(8): key_share0[i]=mmio_read32(AES_KEY_SHARE0_BASE+4*i); key_share1[i]=mmio_read32(AES_KEY_SHARE1_BASE+4*i); key=[a^b for a,b in zip(key_share0,key_share1)]</t>
+          <t>poc/aes_key_disclosure_and_regwen_bypass/tb.sv -&gt; reg_rdata_next==key_share0_0_q (0xCAFEF00D) confirmed; run.sh (self-contained, no deps)</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ctrl_aux_shadowed_gated_we no longer ANDed with ctrl_aux_regwen_qs; CTRL_AUX_SHADOWED (incl. key_touch_forces_reseed) stays writable forever, even after firmware clears the REGWEN lock.</t>
+          <t>ctrl_aux_shadowed_gated_we no longer ANDed with ctrl_aux_regwen_qs; CTRL_AUX_SHADOWED (incl. key_touch_forces_reseed) stays writable after firmware clears the REGWEN lock.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/01_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED (same testbench as Bug 1)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Attacker/malicious code can re-enable or weaken AES SCA hardening settings after boot-time lockdown, undermining the write-once security configuration model</t>
+          <t>Attacker/malicious code can re-enable or weaken AES SCA hardening settings after boot-time lockdown</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>mmio_write32(AES_CTRL_AUX_REGWEN, 0); mmio_write32(AES_CTRL_AUX_SHADOWED, 0x0); // still succeeds, should be rejected</t>
+          <t>poc/aes_key_disclosure_and_regwen_bypass/tb.sv -&gt; with regwen_qs=0, gated_we_buggy=1 vs gated_we_correct=0 confirmed; run.sh</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Dynamic: Verilator PoC (poc/mubi4_fault_injection/tb.sv) exhaustively drives all 16 values and shows 4'h7 mismatches spec; static diff evidence/02_...diff</t>
+          <t>DYNAMICALLY CONFIRMED: Verilator PoC exhaustively drives all 16 values, shows 4'h7 mismatches spec</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Defeats the multibit fault-injection countermeasure used throughout the design (KMAC/SHA3 done_i gating, lifecycle escalation checks, etc.); a single-bit glitch can be accepted as a legitimate True security decision</t>
+          <t>Defeats the multibit fault-injection countermeasure used throughout the design (e.g. KMAC/SHA3 done_i gating)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Restore exact equality check (val==MuBi4True); add CI lint rule forbidding XOR/inside-range rewrites of mubi4_test_*_strict; re-run formal SVA for CheckMuBi4ValsComplementary</t>
+          <t>Restore exact equality check (val==MuBi4True); add CI lint forbidding XOR/inside-range rewrites of mubi4_test_*_strict</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>poc/mubi4_fault_injection/tb.sv -&gt; glitched = MuBi4True ^ 4'h1; assert(mubi4_test_true_strict(glitched)==1) // PASSES, proving bypass</t>
+          <t>poc/mubi4_fault_injection/tb.sv -&gt; glitched=MuBi4True^4'h1; mubi4_test_true_strict(glitched)==1 CONFIRMED; run.sh (self-contained)</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/03_...diff); algebraic proof via De Morgan's law</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED with a full AHB-Lite Verilator testbench against the real spi_host_reg_top.sv</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Denial of service (SPI host disabled or reset mid-transaction, e.g. during boot SPI-flash reads) and silent corruption of RX/TX watermark thresholds via a write to an address that should be inert</t>
+          <t>Denial of service (SPI host disabled/reset mid-transaction, e.g. during boot SPI-flash reads) and silent corruption of RX/TX watermark thresholds</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Restore control_we = addr_hit[4] &amp; reg_we &amp; !reg_error (single-bit qualifier only); add regression test writing STATUS and asserting CONTROL unchanged</t>
+          <t>Restore control_we = addr_hit[4] &amp; reg_we &amp; !reg_error (single-bit qualifier only)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ahb_write(SPI_HOST_STATUS_OFFSET, 0xC0000000); // bit31 clears SPIEN, bit30 asserts SW_RST as a side effect</t>
+          <t>poc/spi_host_control_we_aliasing/tb.sv -&gt; write STATUS=0x40000000 flips CONTROL from 0x80001122 to 0x40000000 (SPIEN cleared, SW_RST set); run.sh</t>
         </is>
       </c>
     </row>
@@ -774,22 +774,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>aes_only_to_key_release rule gated additionally on !kv_data0_present (author-labeled BUG 1A); when a non-AES engine's write is KV-forwarded (kv_data0_present=1), the rule silently passes.</t>
+          <t>aes_only_to_key_release rule additionally gated on !kv_data0_present (author-labeled BUG 1A); a non-AES engine's KV-forwarded write (kv_data0_present=1) to the release slot silently passes.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>src/keyvault/rtl/kv_write_rule_check.sv, release_slot_source_from_raw / eval_aes_only_to_key_release</t>
+          <t>src/keyvault/rtl/kv_write_rule_check.sv, release_slot_source_from_raw</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2; challenge author's own '// BUG 1A' comment left in source (evidence/04_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; author's own '// BUG 1A' comment; DYNAMICALLY CONFIRMED via differential test (real DUT vs a golden spec model) in Verilator</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>A non-AES crypto engine can write attacker-influenced data into OCP_LOCK_KEY_RELEASE_KV_SLOT during OCP-Lock provisioning, corrupting or substituting the release key</t>
+          <t>A non-AES crypto engine can write attacker-influenced data into OCP_LOCK_KEY_RELEASE_KV_SLOT during OCP-Lock provisioning</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Remove the kv_data0_present qualifier from the rule so ANY non-AES source write to the release slot fails, regardless of forwarding path</t>
+          <t>Remove the kv_data0_present qualifier so any non-AES source write to the release slot fails regardless of forwarding path</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>// during ocp_lock_in_progress, program HMAC (non-AES) to KV-forward-write OCP_LOCK_KEY_RELEASE_KV_SLOT with kv_data0_present=1 -&gt; write_allow asserts despite rule</t>
+          <t>poc/kv_write_rule_check_bugs/tb.sv -&gt; HMAC write to release slot with kv_data0_present=1: DUT write_allow=1, golden=0 (SECURITY BYPASS); run.sh</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Key Vault region isolation: OCP-Lock-region data must stay in LOCK region</t>
+          <t>Key Vault region isolation: STD-region destination boundary check</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>dst_in_std_region upper bound changed to KV_STANDARD_SLOT_HI-1 (author-labeled BUG 1C); the last STD slot is excluded from the STD-region check, letting LOCK-region source data be written there without tripping std_to_std.</t>
+          <t>dst_in_std_region upper bound changed to KV_STANDARD_SLOT_HI-1 (author-labeled BUG 1C). Exhaustive differential testing (real DUT vs golden model) shows this makes the RTL OVER-block a legitimate STD-to-STD-boundary write (dst=slot 15) rather than open a confidentiality bypass -- no combination of LOCK-region source + this destination produces a bypass, because rule (c) lock_to_lock independently and correctly blocks that case regardless of this bug.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -846,37 +846,37 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2; challenge author's own '// BUG 1C' comment left in source (evidence/04_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; author's own '// BUG 1C' comment; DYNAMICALLY VERIFIED via exhaustive differential sweep (10 directed cases incl. dual-source) in Verilator -- reclassified from confidentiality bypass to availability/over-block after dynamic testing contradicted the initial static-read hypothesis</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>OCP-Lock-region secret data can be committed into the boundary slot of the standard region, which ordinary (non-privileged) crypto clients are allowed to read, leaking LOCK-region secrets</t>
+          <t>A legitimate STD-source write targeting the STD region's own top slot (KV_STANDARD_SLOT_HI) is incorrectly REJECTED (false-positive rule failure) -- an availability/correctness defect, not a confidentiality leak</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Local firmware/attacker able to trigger a KV write with a LOCK-region source and kv_write_entry == KV_STANDARD_SLOT_HI during ocp_lock_in_progress</t>
+          <t>N/A for exploitation (no attacker benefit); affects any firmware flow that legitimately writes the boundary STD slot during OCP-Lock provisioning</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Restore inclusive upper bound KV_STANDARD_SLOT_HI in dst_in_std_region; add boundary-slot directed test</t>
+          <t>Restore inclusive upper bound KV_STANDARD_SLOT_HI in dst_in_std_region</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7.1 / High</t>
+          <t>4.0 / Medium (availability only; corrected down from initial confidentiality-bypass hypothesis after dynamic testing)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:N/S:C/C:H/I:N/A:N</t>
+          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:L</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>kv_write(entry=KV_STANDARD_SLOT_HI, src=KV_OCP_LOCK_SLOT_LOW) while ocp_lock_in_progress=1 -&gt; std_to_std never fires, secret lands in a std-readable slot</t>
+          <t>poc/kv_write_rule_check_bugs/tb.sv -&gt; full boundary + dual-source sweep: only mismatch is DUT=0/golden=1 at dst=15 (over-block, not a bypass); run.sh</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>no_read_key_release rule changed from exact-match (kv_read_dest != DMA-only-onehot) to bitwise overlap (dest_selects_dma = OR(dest &amp; DMA_mask)); a concurrent non-DMA reader alongside a DMA reader is no longer flagged.</t>
+          <t>no_read_key_release rule changed from exact-match (kv_read_dest != DMA-only-onehot) to bitwise overlap; a concurrent non-DMA reader alongside a DMA reader of the same slot is no longer flagged.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/05_...diff); traced kv_read_dest as a multi-client bitmask via kv_defines_pkg.sv (KV_NUM_READ=9)</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED via differential test (real DUT vs golden exact-match model) in Verilator</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>A non-DMA crypto engine (e.g. HMAC) can read the OCP-Lock release key concurrently with a DMA read of the same slot, exfiltrating a secret that policy restricts to the DMA extraction path only</t>
+          <t>A non-DMA crypto engine (e.g. HMAC, ECC) can read the OCP-Lock release key concurrently with a DMA read of the same slot, exfiltrating a secret policy restricts to the DMA extraction path only</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Restore exact-match check (kv_read_dest == DMA-only one-hot, i.e. no other bit may be set) instead of bitwise overlap</t>
+          <t>Restore exact-match check (kv_read_dest == DMA-only one-hot, no other bit may be set)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>issue HMAC read of OCP_LOCK_KEY_RELEASE_KV_SLOT simultaneously with a DMA read of the same entry -&gt; read_allow asserts for both, HMAC observes release key material</t>
+          <t>poc/kv_read_rule_check_bypass/tb.sv -&gt; concurrent DMA+HMAC and DMA+ECC_SEED reads of release slot: DUT=1, golden=0 (SECURITY BYPASS) x2; run.sh</t>
         </is>
       </c>
     </row>
@@ -960,47 +960,47 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Read mux hardcodes pv_read[0].read_entry/read_offset for every client's pv_rd_resp[client] instead of pv_read[client]; every PCR read port returns data selected by client 0's request.</t>
+          <t>Read mux hardcodes pv_read[0] for every pv_rd_resp[client] instead of pv_read[client]. HOWEVER: dynamic testing also found this source drop separately shrank pv_defines_pkg.sv's PV_NUM_READ from the upstream default of 2 down to 1, and only ONE consumer (sha512.sv) is wired to pv anywhere in the design -- with a single client, pv_read[0]==pv_read[client] trivially, so the hardcoded index has NO observable effect in the shipped configuration. It is a live cross-client leak only if a second PCR read client is ever wired up (upstream's own default topology).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>src/pcrvault/rtl/pv.sv, keyvault_readmux always_comb block</t>
+          <t>src/pcrvault/rtl/pv.sv, keyvault_readmux; src/pcrvault/rtl/pv_defines_pkg.sv (PV_NUM_READ 2-&gt;1)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/06_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY VERIFIED both states in Verilator: NUM_READ=1 (shipped) shows no leak, NUM_READ=2 (upstream default) shows the identical code leaking client 0's PCR entry to client 1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Any PCR read client receives whatever PCR entry client 0 is currently reading instead of its own requested entry, causing cross-client PCR data disclosure/confusion (compounded by Bug 15-adjacent pv_gen_hash.sv zeroize gap)</t>
+          <t>No impact in the configuration as currently shipped (single read client). Re-introducing a second PCR read client (matching upstream's own default) would immediately and silently leak one client's PCR entry to another.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Local firmware/engine acting as a PCR read client while another (client 0) is mid-read of a different, more sensitive PCR entry</t>
+          <t>N/A currently exploitable; latent defect that would activate for whichever team next re-enables a second PCR consumer without re-auditing this file</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Restore per-client indexing pv_read[client] in the read-mux loop; add multi-client concurrent-read regression test</t>
+          <t>Restore per-client indexing pv_read[client] in the read-mux loop regardless of current PV_NUM_READ, so the code is safe if/when a second client returns</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7.1 / High</t>
+          <t>N/A (not exploitable in shipped config) / Low if scored as a latent defect</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:N/S:C/C:H/I:N/A:N</t>
+          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:N (no scorable impact in current build; would be C:H/S:C ~7.1 High if a second read client is added back without fixing the index)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>client3.request(read_entry=5); client0.request(read_entry=2,sensitive); observe pv_rd_resp[3] == data of PCR entry 2, not entry 5</t>
+          <t>poc/pv_read_mux_client0_hardcode/tb.sv -&gt; NUM_READ=1: correct; NUM_READ=2: client1 receives client0's entry (BUG CONFIRMED, latent); run.sh</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SHA-256 digest register scrub-on-debug-unlock</t>
+          <t>SHA-256 digest register availability</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>hwclr for SHA256_DIGEST driven by zeroize_reg2 = ZEROIZE | ~debugUnlock_or_scan_mode_switch instead of zeroize_reg = ZEROIZE | debugUnlock_or_scan_mode_switch; digest is not force-cleared on a debug-unlock/scan-mode transition without explicit SW ZEROIZE.</t>
+          <t>DIGEST.hwclr driven by zeroize_reg2 = ZEROIZE | ~debugUnlock_or_scan_mode_switch instead of zeroize_reg = ZEROIZE | debugUnlock_or_scan_mode_switch. Dynamic testing (running an actual hash through the real register interface) shows this is NOT the 'stale secret retained after debug' leak a static read suggests: in normal (debug-locked, D=0) operation, zeroize_reg2 is UNCONDITIONALLY 1 regardless of software's ZEROIZE bit, so SHA256_DIGEST is hardware-cleared every cycle and can never show a result at all -- even though the core's own internal digest_reg computes the correct value. With debug open (D=1) the core is separately held in reset by the still-correct zeroize_reg, so no computation completes there either. Net effect: SHA256_DIGEST read-back is unconditionally non-functional in every reachable state.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1032,37 +1032,37 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/07_...diff); boolean identity check (De Morgan) of the two expressions</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY TESTED end-to-end (real hash op through the real register interface, both debug-locked and debug-open) in Verilator -- reclassified from a confidentiality leak to a permanent availability failure after the static hypothesis did not survive dynamic testing</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Digest of a pre-unlock SHA-256 operation over secret-derived input remains readable through SHA256_DIGEST registers after a debug session opens</t>
+          <t>Complete, permanent denial-of-service of the SHA-256 digest read-back path -- firmware can never retrieve a SHA-256 result via SHA256_DIGEST, which would break any boot-measurement/attestation flow depending on this accelerator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Physical adversary who can trigger a debug-unlock or scan-mode transition (JTAG/test access) shortly after a sensitive hash operation</t>
+          <t>N/A as a confidentiality exploit; relevant as a functional/availability defect discovered by any integration test that reads back a SHA-256 result</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Restore DIGEST.hwclr = zeroize_reg (drop the zeroize_reg2 split); add SVA that DIGEST==0 one cycle after debugUnlock_or_scan_mode_switch</t>
+          <t>Restore DIGEST.hwclr = zeroize_reg (drop the zeroize_reg2 split); add a directed test that reads back a nonzero digest after a normal hash op</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5.3 / Medium</t>
+          <t>6.2 / Medium</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:P/AC:L/PR:N/UI:N/S:C/C:H/I:N/A:N</t>
+          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>run sha256(secret_block); assert digest_reg!=0; assert_debug_unlock(); read SHA256_DIGEST[0..7] -&gt; still equals pre-unlock digest instead of 0</t>
+          <t>poc/sha256_digest_hwclr_bypass/tb.sv -&gt; internal digest_reg=0xe3c455e4... (real result) but SHA256_DIGEST reads back 0x0 in both debug-locked and debug-open scenarios; run.sh</t>
         </is>
       </c>
     </row>
@@ -1079,52 +1079,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SHA-512 digest register scrub-on-debug-unlock</t>
+          <t>SHA-512 digest register availability</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Identical bug to Bug 9, duplicated in the SHA-512 core: DIGEST.hwclr driven by zeroize_reg2 instead of zeroize_reg, so digest survives a debug-unlock/scan-mode transition.</t>
+          <t>Identical construct to Bug 9, duplicated in the SHA-512 core (zeroize_reg2 used for SHA512_DIGEST.hwclr while the core's own internal reset still correctly uses zeroize_reg). Not independently re-simulated end-to-end (sha512.sv pulls in Key-Vault/PCR-Vault ports beyond scope for this pass) but the exact same code pattern is verified byte-for-byte identical via diff, so the same dynamically-confirmed conclusion applies by direct code-structure equivalence.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>src/sha512/rtl/sha512.sv, zeroize_reg/zeroize_reg2 and DIGEST.hwclr assignment</t>
+          <t>src/sha512/rtl/sha512.sv, zeroize_reg/zeroize_reg2 and SHA512_DIGEST.hwclr assignment (SHA512_GEN_PCR_HASH_DIGEST.hwclr is unaffected, still uses zeroize_reg correctly)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/08_...diff)</t>
+          <t>Static diff vs upstream v2.1.2, confirmed byte-identical in structure to the dynamically-tested Bug 9 pattern</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Digest of a pre-unlock SHA-512/384 operation (e.g. over UDS/FE-derived or HMAC-chained secret data) remains readable through SHA512_DIGEST after debug-unlock</t>
+          <t>Same as Bug 9: permanent denial-of-service of the SHA-512 digest read-back path in normal operation</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Physical adversary who can trigger a debug-unlock or scan-mode transition shortly after a sensitive hash operation</t>
+          <t>N/A as a confidentiality exploit; functional/availability defect</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Restore DIGEST.hwclr = zeroize_reg; add SVA that DIGEST==0 one cycle after debugUnlock_or_scan_mode_switch</t>
+          <t>Restore DIGEST.hwclr = zeroize_reg (drop the zeroize_reg2 split)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5.3 / Medium</t>
+          <t>6.2 / Medium</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:P/AC:L/PR:N/UI:N/S:C/C:H/I:N/A:N</t>
+          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>run sha512(secret_block); assert digest_reg!=0; assert_debug_unlock(); read SHA512_DIGEST[0..15] -&gt; still equals pre-unlock digest instead of 0</t>
+          <t>Not separately simulated -- see poc/sha256_digest_hwclr_bypass/ for the dynamically-confirmed identical code pattern; evidence/08_sha512_digest_hwclr_bypass.diff for the byte-identical construct</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>SS_DEBUG_INTENT.debug_intent.we De Morgan-rewritten with inverted polarity: write now succeeds when cptra_uncore_dmi_unlocked_reg_wr_en is 0 (DMI locked/unauthenticated) and is blocked when it is 1 (properly unlocked).</t>
+          <t>SS_DEBUG_INTENT.debug_intent.we De Morgan-rewritten with inverted polarity: write succeeds when cptra_uncore_dmi_unlocked_reg_wr_en is 0 (DMI locked/unauthenticated) and is blocked when it is 1 (properly unlocked).</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/09_...diff); De Morgan algebraic proof of polarity inversion</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED with an exhaustive 4-case truth-table test of the exact patched boolean expression in Verilator</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>An unauthenticated party on the DMI/JTAG TAP can set the subsystem debug-intent strap that boot firmware consults to decide whether to grant debug access, without completing the unlock/authentication sequence</t>
+          <t>An unauthenticated party on the DMI/JTAG TAP can set the subsystem debug-intent strap that boot firmware consults to grant debug access, without completing the unlock/authentication sequence</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>over JTAG, without completing DMI unlock: dmi_write(DMI_REG_SS_DEBUG_INTENT, 1) -&gt; write succeeds (should be blocked while dmi_unlocked_reg_wr_en==0)</t>
+          <t>poc/soc_ifc_top_debug_intent_polarity/tb.sv -&gt; exhaustive 4-case sweep: 2/4 mismatches, incl. we_buggy=1/we_correct=0 with DMI locked+addr==target; run.sh (self-contained)</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/10_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED against the real csrng_state_db.sv module in Verilator</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Any other CSRNG application instance's internal DRBG state (V, key, reseed counter) can be dumped as long as application 0's own debug-read-enable bit happens to be set, breaking per-application confidentiality isolation and enabling prediction of another domain's randomness</t>
+          <t>Any other CSRNG application instance's internal DRBG state (V, key, reseed counter) can be dumped as long as app 0's own debug-read-enable bit is set, breaking per-application confidentiality isolation</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Restore per-index gating: internal_states_dump[rd] = int_st_dump_sel[rd] &amp;&amp; int_state_read_enable_i[rd] (drop the [0]-only broadcast)</t>
+          <t>Restore per-index gating: internal_states_dump[rd] = int_st_dump_sel[rd] &amp;&amp; int_state_read_enable_i[rd]</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>set int_state_read_enable_i[0]=1; set int_st_dump_id_q=N (N!=0); read internal_states_dump -&gt; reveals app N's internal DRBG state despite int_state_read_enable_i[N]==0</t>
+          <t>poc/csrng_state_db_cross_instance/tb.sv -&gt; app0 enable=1, app2 enable=0, dump target=app2: internal_states_dump[2]==app2's real secret state 0xDEADBEEF... (CONFIRMED); run.sh</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>kv_write.write_dest_valid for the UDS derivation path changed from 'd3 (bits 0,1) to 9'h023 (bits 0,1,5), granting an additional hardware engine (KV_DEST_IDX bit 5) read access to the Unique Device Secret-derived key that other derivations (FE) do not get.</t>
+          <t>kv_write.write_dest_valid for the UDS derivation path changed from 'd3 (bits 0,1) to 9'h023 (bits 0,1,5 = KV_DEST_IDX_AES_KEY), granting the AES engine's Key-Vault read port direct access to the Unique Device Secret-derived key that other derivations (e.g. Field Entropy) do not get.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/12_...diff); cross-referenced KV_NUM_READ/KV_DEST_IDX_* in kv_defines_pkg.sv</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED by exercising the exact patched mux expression in Verilator; bit 5 identity (KV_DEST_IDX_AES_KEY) cross-referenced from kv_defines_pkg.sv</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>An additional crypto engine gains direct Key-Vault read access to the device's Unique Device Secret-derived key material, widening the set of components that can extract or misuse the most sensitive per-device secret in the root of trust</t>
+          <t>The AES engine gains direct Key-Vault read access to the device's Unique Device Secret-derived key material, widening the set of components able to extract or misuse the most sensitive per-device secret</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Local firmware able to trigger the engine mapped to KV_DEST_IDX bit 5 to read the UDS-derived KV slot after DOE completes UDS derivation</t>
+          <t>Local firmware able to trigger the AES engine to read the UDS-derived KV slot after DOE completes UDS derivation</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Restore write_dest_valid='d3 for the running_uds case (remove the extra bit-5 grant), or provide explicit justification/gating if bit 5 access is intentionally required</t>
+          <t>Restore write_dest_valid='d3 for the running_uds case, or provide explicit justification/gating if AES access is intentionally required</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>trigger DOE running_uds derivation; engine at KV_DEST_IDX==5 issues KV read of the resulting slot -&gt; read succeeds (should be restricted to the original 2 consumers only)</t>
+          <t>poc/doe_fsm_uds_dest_widening/tb.sv -&gt; UDS path sets write_dest_valid bit 5 (AES_KEY) which the non-UDS path does not (0x23 vs 0x3); run.sh (self-contained)</t>
         </is>
       </c>
     </row>
@@ -1342,17 +1342,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/13_...diff); De Morgan proof (user_from_read = r_win &amp; ~w_dv)</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED against the real axi_sub_arb.sv module in Verilator (drove r_pri to 1 via a completed write burst, then asserted concurrent read+write)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Downstream logic that keys access-control or attribution decisions off the AXI user sideband (source/context ID) can be fed a mismatched tag by keeping an unrelated write pending, potentially bypassing user-based privilege checks on the shared fabric</t>
+          <t>Downstream logic keying access-control/attribution decisions off the AXI user sideband can be fed a mismatched tag by keeping an unrelated write pending, potentially bypassing user-based privilege checks on the shared fabric</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Local bus master able to issue a read of interest for address A while concurrently keeping a write to address B pending on the same arbiter</t>
+          <t>Local bus master able to issue a read of interest for address A while concurrently holding a write to address B pending on the same arbiter</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>issue read(addr=protected) that wins arbitration (r_win=1) while simultaneously holding write(user=privileged_id) pending (w_dv=1) -&gt; outgoing read reports user=privileged_id instead of the real (unprivileged) requester id</t>
+          <t>poc/axi_sub_arb_user_desync/tb.sv -&gt; read(addr=0x12345678,user=0xAA) wins arbitration (write=0) but user=0xFFFFFFFF (the concurrent write's id); run.sh</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>lfsr_seed_reg &lt;= '0 on zeroize removed (author comment left in: 'without zeroize to make it more complex'); the masking LFSR seed feeding sca_entropy is no longer cleared across zeroize boundaries.</t>
+          <t>lfsr_seed_reg &lt;= '0 on zeroize removed (author comment left in: 'without zeroize to make it more complex'); the masking LFSR seed feeding sca_entropy is no longer cleared across zeroize boundaries, while every sibling register (lambda_reg, scalar_rnd_reg, masking_rnd_reg, drbg_reg) is correctly cleared.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1404,22 +1404,22 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2; challenge author's own comment left in source (evidence/14_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; author's own comment left in source; DYNAMICALLY CONFIRMED by reproducing the exact reg_update always_ff block verbatim in Verilator</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Masking randomness that de-correlates power/EM traces across ECDSA sign operations is no longer refreshed at zeroize boundaries, weakening resistance to differential power/EM analysis of the ECDSA private key</t>
+          <t>Masking randomness that de-correlates power/EM traces across ECDSA sign operations is not refreshed at zeroize boundaries, weakening resistance to differential power/EM analysis of the ECDSA private key</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Physical adversary with power/EM side-channel measurement equipment (oscilloscope + probe) capturing multiple ECDSA operations separated by zeroize</t>
+          <t>Physical adversary with power/EM side-channel measurement equipment capturing multiple ECDSA operations separated by zeroize</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Restore lfsr_seed_reg &lt;= '0 on the zeroize branch; add DV check that mask-seed changes across every zeroize event</t>
+          <t>Restore lfsr_seed_reg &lt;= '0 on the zeroize branch</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>capture power traces for ECDSA sign, zeroize, sign again; correlate residual lfsr_seed_reg-derived mask reuse across the two traces via DPA/CPA</t>
+          <t>poc/ecc_hmac_drbg_zeroize_gap/tb.sv -&gt; lambda_reg cleared to 0 by zeroize but lfsr_seed_reg retains 0xDEADBEEF (CONFIRMED); run.sh (self-contained)</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>HMAC512_LFSR_SEED reset default changed from a fixed nonzero value (32'h3cabffb0) to 32'h0; an XOR-feedback LFSR left unseeded starts from (or can get stuck at) the degenerate all-zero state, producing no mask randomness.</t>
+          <t>HMAC512_LFSR_SEED reset default changed from a fixed nonzero value (32'h3cabffb0) to 32'h0; an XOR-feedback LFSR left unseeded starts from the degenerate all-zero state, producing no mask randomness until firmware reseeds it.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/15_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED against the real hmac_reg.sv register block in Verilator</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>If firmware does not explicitly reseed HMAC512_LFSR_SEED before first use, HMAC masking operates with no/degenerate randomness, weakening its power/EM side-channel countermeasure for that window</t>
+          <t>If firmware does not explicitly reseed HMAC512_LFSR_SEED before first use, HMAC masking operates with degenerate (all-zero) randomness for that window, weakening its power/EM side-channel countermeasure</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Restore nonzero reset default 32'h3cabffb0 (or any verified non-degenerate seed); add DV check that mask output is non-zero immediately after reset before any SW reseed</t>
+          <t>Restore nonzero reset default 32'h3cabffb0 (or any verified non-degenerate seed)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>power-on reset HMAC without SW reseed; trigger HMAC op; capture power trace; verify mask sequence is all-zero/degenerate vs expected pseudo-random</t>
+          <t>poc/hmac_lfsr_seed_reset/tb.sv -&gt; all 12 HMAC512_LFSR_SEED words read 0x00000000 post-reset (CONFIRMED); run.sh</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Static diff vs upstream v2.1.2 (evidence/16_...diff)</t>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY DEMONSTRATED the practical consequence by rebuilding the same CALIPTRA_ASSERT_STABLE macro from libs/rtl/caliptra_sva.svh both with and without the assertion present</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>No direct functional/hardware impact by itself, but removes the simulation-time safety net that would have caught a glitch corrupting a key/seed/control register mid-operation (from any of the other bugs above or an unrelated fault), reducing defense-in-depth of the verification flow</t>
+          <t>No direct functional/hardware impact by itself, but removes the simulation-time safety net that would catch a glitch corrupting a key/seed/control register mid-operation (from any of the other bugs above, or an unrelated fault), reducing DV defense-in-depth</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Restore the deleted CALIPTRA_ASSERT_STABLE assertions in all four files; add CI gate rejecting removal of *_NOT_STABLE assertions without explicit design-review sign-off</t>
+          <t>Restore the deleted CALIPTRA_ASSERT_STABLE assertions in all four files; add a CI gate rejecting removal of *_NOT_STABLE assertions without explicit design-review sign-off</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1558,7 +1558,69 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>N/A - verification-only gap; no direct trigger. Re-add assertions and re-run existing testbenches to confirm they still pass (regression, not an exploit)</t>
+          <t>poc/assertion_removal_dv_gap/tb.sv -&gt; identical glitch on key_reg during busy: silent with assertion removed (as shipped) vs $fatal abort with assertion restored; run.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Bug 18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>HW</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Entropy source repetition-count health test (NIST SP 800-90B stuck-bit detector)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>rep_cnt_fail changed from (rep_cntr &gt;= thresh_i) to (rep_cntr &gt; thresh_i) via an algebraically-obfuscated rewrite (threshold_met &amp;&amp; !threshold_equal). A stuck/degenerate noise source that sits exactly at the configured repetition threshold forever escapes detection instead of tripping the health-test failure at that threshold as required.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>src/entropy_src/rtl/entropy_src_repcnts_ht.sv, rep_cnt_fail assignment</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Static diff vs upstream v2.1.2; DYNAMICALLY CONFIRMED against the real entropy_src_repcnts_ht.sv + caliptra_prim_count.sv in Verilator</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>A stuck-at/degenerate TRNG noise source can evade the repetition-count catastrophic-failure health test, allowing predictable/low-entropy randomness to feed CSRNG and downstream key/nonce generation undetected</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Physical adversary able to induce or exploit a degenerate noise-source condition (e.g. via voltage/clock/EM manipulation) that pins the noise source's repeat count at the configured threshold</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Restore rep_cnt_fail = (rep_cntr &gt;= thresh_i)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4.9 / Medium</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:P/AC:H/PR:N/UI:N/S:C/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>poc/entropy_src_repcnt_offbyone/tb.sv -&gt; threshold=5, health-test fires only at rep_cntr=6, not 5 (CONFIRMED); run.sh</t>
         </is>
       </c>
     </row>
